--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/08-delivery-only-kitchen-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/08-delivery-only-kitchen-opening-closing-checklist.xlsx
@@ -677,11 +677,11 @@
     <row r="10">
       <c r="A10" s="5" t="n"/>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="62" customHeight="1">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>▸ Print the shift sheet (opening or closing) or use it on a tablet; the shift manager assigns tasks and each person initials theirs.</t>
+          <t>▸ Print the shift sheet (opening or closing) or use it on a tablet; the shift manager assigns tasks and each person initials theirs. In a shared kitchen facility (a unit in a cloud kitchen park or a commissary), mark N/A what the facility operator handles — alarm, HVAC, restrooms, common areas, driver lobby — and keep your own unit's tasks.</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr"/>
